--- a/02_加值成品/九上/九上2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-2 牛頓第二運動定律　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國三上學期 九上2-2 牛頓第二運動定律　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>牛頓第二定律公式是？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>F=ma</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>合力為零</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>正比</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>合力</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>力等質量乘加速度</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>加速度與合力成？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>反比</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>越大越快加速</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>加速度與質量成？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>正比</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
         <is>
           <t>反比</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>越大越慢</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>加速度方向與什麼相同？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>正比</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>加倍</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>合力</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>同向</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>無合力物體加速度？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>零</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>為零</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>反比</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>小車</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>等速</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>力的單位牛頓等於？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>kg·m/s²</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>摩擦使合力不同進而影響a</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>多力合成計算移高中</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>質量大同引擎力下加速度小</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>導出</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>同力下質量大加速度？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>合力</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>正比</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>小</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>反比</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>要產生加速度需要？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
         <is>
           <t>合力</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>反比</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>合力為零</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
           <t>施力</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>物體加速度方向與合力方向？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>反比</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>相同</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>合力為零</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>合力</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>同向</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>要使物體產生加速度必須施加？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>反比</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>減半</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>合力</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>為零</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>施力</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-2 牛頓第二運動定律　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國三上學期 九上2-2 牛頓第二運動定律　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>質量2kg受力10N,加速度？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>5 m/s²</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>10 N</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>4 m/s²</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>12 N</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>10/2</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>質量4kg加速度3m/s²,力？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>12 N</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>4 m/s²</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>變3倍</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>5 m/s²</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>ma</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>力6N使物體加速2m/s²,質量？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>10 N</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>4m/s</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>4 m/s²</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>3 kg</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>6/2</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>相同力作用大小車,誰加速度大？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>小車</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>反比</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>F=ma</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>質量小</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>質量5kg受20N,加速度？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>變3倍</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>3 kg</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
         <is>
           <t>4 m/s²</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>5 m/s²</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>20/5</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>加速度為零表示合力？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>為零</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>F=ma</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>合力為零</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>力加倍質量不變加速度？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>合力</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>零</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>加倍</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>反比</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>質量加倍力不變加速度？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>F=ma</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>減半</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>反比</t>
         </is>
       </c>
-    </row>
-    <row r="11" ht="34" customHeight="1">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>反比</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>質量3kg受力12N加速度？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>3 kg</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>10 N</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>4 m/s²</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>5 m/s²</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>12/3</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>質量2kg加速度5m/s²所需力？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>12 N</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>4m/s</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
         <is>
           <t>10 N</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>變3倍</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>ma</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國三上學期 九上2-2 牛頓第二運動定律　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國三上學期 九上2-2 牛頓第二運動定律　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>質量2kg受合力8N,3秒後速度變化多少?(由靜止)</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>質量大同引擎力下加速度小</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>質量大需大力才有足夠加速度</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>kg·m/s²</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>12m/s(a=4,v=at)</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>為何滿載卡車起步比空車慢？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
+        <is>
+          <t>質量大需大力才有足夠加速度</t>
+        </is>
+      </c>
+      <c r="D4" s="7" t="inlineStr">
+        <is>
+          <t>摩擦使合力不同進而影響a</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
         <is>
           <t>質量大同引擎力下加速度小</t>
         </is>
       </c>
-      <c r="D4" s="7" t="inlineStr">
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>12m/s(a=4,v=at)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
         <is>
           <t>反比</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>用F=ma解釋火箭為何需巨大推力？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>質量大需大力才有足夠加速度</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>摩擦使合力不同進而影響a</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>12m/s(a=4,v=at)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>多力合成計算移高中</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>同一物體力變3倍加速度如何？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>5 m/s²</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>變3倍</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>12 N</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>4 m/s²</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>正比</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>質量6kg要達2m/s²需多大力？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>12 N</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>5 m/s²</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>4m/s</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>4 m/s²</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>ma</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>推同樣力於冰上與地面加速度差異因？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
         <is>
           <t>摩擦使合力不同進而影響a</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
+          <t>12m/s(a=4,v=at)</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>kg·m/s²</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>多力合成計算移高中</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
+        <is>
           <t>合力</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>物體以等速運動代表受力如何？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>反比</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
         <is>
           <t>合力為零</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>F=ma</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>平衡</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>為何課綱限單一作用力？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>12m/s(a=4,v=at)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>kg·m/s²</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>摩擦使合力不同進而影響a</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>多力合成計算移高中</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>課綱</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>力8N作用4kg物體由靜止2秒後速度？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>3 kg</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>4 m/s²</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
         <is>
           <t>4m/s</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>10 N</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>a=2 v=at</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>同引擎推空車與滿載車誰加速快?為何</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>小</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
         <is>
           <t>空車,質量小</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>為零</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>反比</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/九上/九上2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>力等質量乘加速度</t>
+          <t>力等質量乘加速度：力等於質量乘以加速度,這就是牛頓第二定律的公式</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>越大越快加速</t>
+          <t>越大越快加速：合力越大,物體被推動得越快,加速度也就越大</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>越大越慢</t>
+          <t>越大越慢：質量越大越難推動,同樣的力產生的加速度就越小</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>同向</t>
+          <t>同向：物體加速的方向,會跟作用在它身上的合力方向一致</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>等速</t>
+          <t>等速：完全沒有淨力作用時,速度不會改變,加速度就是零</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>導出</t>
+          <t>導出：牛頓這個力的單位,是由質量公斤乘以加速度公尺每秒平方組合而成</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>反比：用同樣大小的力去推,質量越重的物體加速度會越小</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>施力</t>
+          <t>施力：物體要改變速度快慢,一定要有不為零的合力作用在它身上</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>同向</t>
+          <t>同向：牛頓第二定律指出加速度的方向永遠和作用在物體上的合力方向相同</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>施力</t>
+          <t>施力：物體要改變運動狀態(產生加速度),必須受到不為零的合力作用</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>10/2</t>
+          <t>10/2：力10牛頓除以質量2公斤,等於加速度每秒5公尺每秒</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>ma：質量4公斤乘以加速度3,等於需要的力是12牛頓</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>6/2</t>
+          <t>6/2：力6牛頓除以加速度2,反推出這個物體的質量是3公斤</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>質量小</t>
+          <t>質量小：力一樣大時,質量比較小的車子比較容易被推動,加速度較大</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>20/5</t>
+          <t>20/5：力20牛頓除以質量5公斤,等於加速度每秒4公尺每秒</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：加速度是零代表所有受力互相抵消,合力剛好是零</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：質量沒變,把力變成兩倍,加速度也會跟著變成兩倍</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>反比：力沒變,把質量變成兩倍,加速度就會變成原來的一半</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>12/3</t>
+          <t>12/3：由F=ma可得a=F/m,12牛頓除以3公斤等於4m/s²</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>ma：由F=ma,質量2公斤乘以加速度5m/s²等於10牛頓</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：先算加速度a等於8除以2等於4,再用速度等於加速度乘時間,4乘3等於12公尺每秒</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>反比：引擎輸出的力差不多,但滿載後質量變大很多,所以加速度變小起步較慢</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：火箭本身質量非常大,要達到能升空的加速度,就需要非常巨大的推力</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>正比：質量不變的情況下,力變成三倍,加速度也會等比例變成三倍</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>ma</t>
+          <t>ma：把質量6公斤乘以想要的加速度2,算出需要的力是12牛頓</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>合力</t>
+          <t>合力：冰上摩擦力小、地面摩擦力大,實際的合力不同,所以加速度也不同</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>平衡</t>
+          <t>平衡：速度保持不變表示所有作用力互相抵消,合力為零</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>課綱</t>
+          <t>課綱：多個力同時作用要先合成再計算,這部分較複雜的內容留到高中才教</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>a=2 v=at</t>
+          <t>a=2 v=at：先求加速度a=F/m=8/4=2m/s²,再由v=at,2乘以2秒等於4m/s</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>反比：同樣的推力下,由a=F/m可知質量越小加速度越大,所以空車的質量較小,加速較快</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/九上/九上2-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/九上/九上2-2_三種難度測驗卷.xlsx
@@ -683,12 +683,12 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>正比</t>
+          <t>小</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>加倍</t>
+          <t>F=ma</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
@@ -728,17 +728,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>為零</t>
+          <t>相同</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>F=ma</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>小車</t>
+          <t>減半</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
@@ -803,17 +803,17 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
+          <t>正比</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>合力為零</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
           <t>合力</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="inlineStr">
-        <is>
-          <t>正比</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>相同</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -848,17 +848,17 @@
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>零</t>
+          <t>反比</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>小車</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>合力為零</t>
+          <t>小</t>
         </is>
       </c>
       <c r="G10" s="8" t="inlineStr">
@@ -923,12 +923,12 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>加倍</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>減半</t>
+          <t>F=ma</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>為零</t>
+          <t>小車</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
@@ -1164,17 +1164,17 @@
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>F=ma</t>
         </is>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>減半</t>
         </is>
       </c>
       <c r="F6" s="7" t="inlineStr">
         <is>
-          <t>F=ma</t>
+          <t>正比</t>
         </is>
       </c>
       <c r="G6" s="8" t="inlineStr">
@@ -1244,17 +1244,17 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>相同</t>
+          <t>小車</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>F=ma</t>
+          <t>減半</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>合力為零</t>
+          <t>正比</t>
         </is>
       </c>
       <c r="G8" s="8" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>小</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>正比</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>F=ma</t>
+          <t>空車,質量小</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
@@ -1875,7 +1875,7 @@
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>小</t>
+          <t>減半</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>相同</t>
+          <t>加倍</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>為零</t>
+          <t>反比</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
